--- a/Result/profitability/2542.xlsx
+++ b/Result/profitability/2542.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.78</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8175</v>
+        <v>0.8687499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>30.95625</v>
+        <v>30.35375</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>2.03</v>
       </c>
       <c r="M3" t="n">
-        <v>0.96</v>
+        <v>0.92125</v>
       </c>
       <c r="N3" t="n">
-        <v>29.50625</v>
+        <v>29.01</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.14</v>
       </c>
       <c r="M4" t="n">
-        <v>0.77625</v>
+        <v>0.93875</v>
       </c>
       <c r="N4" t="n">
-        <v>28.025</v>
+        <v>27.105</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
         <v>97.3</v>
@@ -1018,10 +1018,10 @@
         <v>0.44</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8312499999999999</v>
+        <v>0.96375</v>
       </c>
       <c r="N5" t="n">
-        <v>25.75375</v>
+        <v>27.18875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.72</v>
       </c>
       <c r="M6" t="n">
-        <v>0.89125</v>
+        <v>0.96375</v>
       </c>
       <c r="N6" t="n">
-        <v>26.575</v>
+        <v>27.15</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.96</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04625</v>
+        <v>1.065</v>
       </c>
       <c r="N7" t="n">
-        <v>27</v>
+        <v>26.80625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.92</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1425</v>
+        <v>1.16125</v>
       </c>
       <c r="N8" t="n">
-        <v>26.5575</v>
+        <v>26.775</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>17045</v>
+      </c>
+      <c r="D75" t="n">
+        <v>11617</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5428</v>
+      </c>
+      <c r="F75" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4318</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>25.33%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>274</v>
+      </c>
+      <c r="J75" t="n">
+        <v>4592</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2746</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.8825000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.835</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1304347826086958</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.740000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.05778811026237141</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>4.416666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.563573883161512</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
